--- a/Theo dõi/Theo dõi xe chạy hôm nay/Danh sách xe.xlsx
+++ b/Theo dõi/Theo dõi xe chạy hôm nay/Danh sách xe.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F16EEB5-26F8-4CC3-B95B-2D3670592454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B43DC5-E70D-415A-8DCB-155842A71FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nam đảo" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="84">
   <si>
     <t/>
   </si>
@@ -285,6 +285,9 @@
   <si>
     <t>chưa đi làm</t>
   </si>
+  <si>
+    <t>K12105 164</t>
+  </si>
 </sst>
 </file>
 
@@ -449,17 +452,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2584,41 +2587,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
     </row>
     <row r="2" spans="1:36" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -2659,43 +2662,43 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -3271,41 +3274,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
     </row>
     <row r="2" spans="1:36" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -3346,43 +3349,43 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
@@ -3451,7 +3454,7 @@
       <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="4">
@@ -3471,7 +3474,7 @@
       <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="13" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="4">
@@ -3491,7 +3494,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="13"/>
       <c r="D7" s="4">
         <v>334409417</v>
       </c>
@@ -3507,7 +3510,7 @@
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="4">
         <v>943543909</v>
       </c>
@@ -3523,7 +3526,7 @@
       <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D9" s="4">
@@ -3543,7 +3546,7 @@
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="4">
@@ -3563,7 +3566,7 @@
       <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="13" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="4">
@@ -3583,7 +3586,7 @@
       <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="13" t="s">
         <v>66</v>
       </c>
       <c r="D12" s="4"/>
@@ -3601,7 +3604,7 @@
       <c r="B13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="4"/>
@@ -3619,7 +3622,7 @@
       <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="13" t="s">
         <v>40</v>
       </c>
       <c r="D14" s="4">
@@ -3639,7 +3642,7 @@
       <c r="B15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="4">
@@ -3668,7 +3671,7 @@
       <c r="B16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="13" t="s">
         <v>42</v>
       </c>
       <c r="D16" s="4">
@@ -3688,7 +3691,7 @@
       <c r="B17" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="13" t="s">
         <v>53</v>
       </c>
       <c r="D17" s="4"/>
@@ -3706,7 +3709,7 @@
       <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="15"/>
+      <c r="C18" s="13"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="3"/>
@@ -3720,7 +3723,7 @@
       <c r="B19" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="13" t="s">
         <v>70</v>
       </c>
       <c r="D19" s="4">
@@ -3740,7 +3743,7 @@
       <c r="B20" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="13" t="s">
         <v>67</v>
       </c>
       <c r="D20" s="4"/>
@@ -3758,7 +3761,7 @@
       <c r="B21" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D21" s="4">
@@ -3778,7 +3781,7 @@
       <c r="B22" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="14" t="s">
         <v>72</v>
       </c>
       <c r="D22" s="4"/>
@@ -3794,7 +3797,7 @@
       <c r="B23" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="15"/>
+      <c r="C23" s="13"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="3"/>
@@ -3808,7 +3811,7 @@
       <c r="B24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D24" s="4"/>
@@ -3826,7 +3829,7 @@
       <c r="B25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="13" t="s">
         <v>56</v>
       </c>
       <c r="D25" s="4"/>
@@ -3844,7 +3847,7 @@
       <c r="B26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="15"/>
+      <c r="C26" s="13"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="3"/>
@@ -3856,9 +3859,9 @@
         <v>23</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="4"/>
@@ -3879,7 +3882,7 @@
       <c r="B28" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D28" s="4">
@@ -3902,7 +3905,7 @@
       <c r="B29" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="14" t="s">
         <v>80</v>
       </c>
       <c r="D29" s="4"/>
@@ -3920,7 +3923,7 @@
       <c r="B30" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="16"/>
+      <c r="C30" s="14"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
         <v>50</v>
@@ -3936,7 +3939,7 @@
       <c r="B31" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="16"/>
+      <c r="C31" s="14"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="3"/>
@@ -3950,7 +3953,7 @@
       <c r="B32" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="13" t="s">
         <v>76</v>
       </c>
       <c r="D32" s="4"/>
@@ -3968,7 +3971,7 @@
       <c r="B33" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="14" t="s">
         <v>43</v>
       </c>
       <c r="D33" s="4"/>
@@ -4065,41 +4068,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
     </row>
     <row r="2" spans="1:36" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -4140,43 +4143,43 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
@@ -4756,41 +4759,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
     </row>
     <row r="2" spans="1:36" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -4831,43 +4834,43 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
@@ -5449,41 +5452,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
     </row>
     <row r="2" spans="1:36" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -5524,43 +5527,43 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
@@ -6175,41 +6178,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
     </row>
     <row r="2" spans="1:36" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -6250,43 +6253,43 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
@@ -6914,41 +6917,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
     </row>
     <row r="2" spans="1:36" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -6989,43 +6992,43 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
@@ -7653,41 +7656,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
     </row>
     <row r="2" spans="1:36" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -7728,43 +7731,43 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
@@ -8459,41 +8462,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
     </row>
     <row r="2" spans="1:36" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -8534,43 +8537,43 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
@@ -9263,41 +9266,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
     </row>
     <row r="2" spans="1:36" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -9338,43 +9341,43 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
@@ -9443,7 +9446,7 @@
       <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="4">
@@ -9463,7 +9466,7 @@
       <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="13" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="4">
@@ -9483,7 +9486,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="13"/>
       <c r="D7" s="4">
         <v>334409417</v>
       </c>
@@ -9499,7 +9502,7 @@
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="4">
         <v>943543909</v>
       </c>
@@ -9515,7 +9518,7 @@
       <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D9" s="4">
@@ -9535,7 +9538,7 @@
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="4">
@@ -9555,7 +9558,7 @@
       <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="13" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="4">
@@ -9575,7 +9578,7 @@
       <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="13" t="s">
         <v>66</v>
       </c>
       <c r="D12" s="4"/>
@@ -9593,7 +9596,7 @@
       <c r="B13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="4"/>
@@ -9611,7 +9614,7 @@
       <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="13" t="s">
         <v>40</v>
       </c>
       <c r="D14" s="4">
@@ -9631,7 +9634,7 @@
       <c r="B15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="4">
@@ -9660,7 +9663,7 @@
       <c r="B16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="13" t="s">
         <v>42</v>
       </c>
       <c r="D16" s="4">
@@ -9680,7 +9683,7 @@
       <c r="B17" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="13" t="s">
         <v>53</v>
       </c>
       <c r="D17" s="4"/>
@@ -9698,7 +9701,7 @@
       <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="15"/>
+      <c r="C18" s="13"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="3"/>
@@ -9712,7 +9715,7 @@
       <c r="B19" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="13" t="s">
         <v>70</v>
       </c>
       <c r="D19" s="4">
@@ -9732,7 +9735,7 @@
       <c r="B20" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="13" t="s">
         <v>67</v>
       </c>
       <c r="D20" s="4"/>
@@ -9750,7 +9753,7 @@
       <c r="B21" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D21" s="4">
@@ -9770,7 +9773,7 @@
       <c r="B22" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="14" t="s">
         <v>72</v>
       </c>
       <c r="D22" s="4"/>
@@ -9786,7 +9789,7 @@
       <c r="B23" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="15"/>
+      <c r="C23" s="13"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="3"/>
@@ -9800,7 +9803,7 @@
       <c r="B24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D24" s="4"/>
@@ -9818,7 +9821,7 @@
       <c r="B25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="13" t="s">
         <v>56</v>
       </c>
       <c r="D25" s="4"/>
@@ -9836,7 +9839,7 @@
       <c r="B26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="15"/>
+      <c r="C26" s="13"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="3"/>
@@ -9850,7 +9853,7 @@
       <c r="B27" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="4"/>
@@ -9871,7 +9874,7 @@
       <c r="B28" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D28" s="4">
@@ -9894,7 +9897,7 @@
       <c r="B29" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="14" t="s">
         <v>80</v>
       </c>
       <c r="D29" s="4"/>
@@ -9912,7 +9915,7 @@
       <c r="B30" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="16"/>
+      <c r="C30" s="14"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
         <v>50</v>
@@ -9928,7 +9931,7 @@
       <c r="B31" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="16"/>
+      <c r="C31" s="14"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="3"/>
@@ -9942,7 +9945,7 @@
       <c r="B32" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="13" t="s">
         <v>76</v>
       </c>
       <c r="D32" s="4"/>
@@ -9960,7 +9963,7 @@
       <c r="B33" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="14" t="s">
         <v>43</v>
       </c>
       <c r="D33" s="4"/>
